--- a/output/福島赤十字病院_随意契約_X線関連.xlsx
+++ b/output/福島赤十字病院_随意契約_X線関連.xlsx
@@ -742,7 +742,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（令和7年4月1日〜）</t>
+          <t>不明（令和7年4月1日〜令和7年9月16日）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
